--- a/data/trans_dic/IMC_inf_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 39,5</t>
+          <t>23,35; 40,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,43; 54,56</t>
+          <t>34,96; 54,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,21; 68,61</t>
+          <t>45,99; 69,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,86; 55,24</t>
+          <t>20,87; 55,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,72; 59,26</t>
+          <t>41,17; 60,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,21; 56,71</t>
+          <t>36,8; 58,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,54; 63,51</t>
+          <t>41,09; 64,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,08; 47,57</t>
+          <t>23,51; 47,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,34; 46,76</t>
+          <t>33,27; 46,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,83; 52,33</t>
+          <t>38,32; 52,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,17; 63,29</t>
+          <t>47,4; 62,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,79; 46,56</t>
+          <t>27,05; 46,71</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,81; 40,11</t>
+          <t>31,65; 40,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,1; 46,87</t>
+          <t>38,12; 46,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,27; 38,36</t>
+          <t>29,75; 38,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,58; 32,98</t>
+          <t>22,41; 33,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,44; 52,36</t>
+          <t>44,73; 52,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,05; 55,9</t>
+          <t>47,04; 55,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,25; 47,89</t>
+          <t>39,56; 48,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,12; 47,73</t>
+          <t>36,86; 46,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,62; 45,16</t>
+          <t>39,69; 45,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,36; 50,3</t>
+          <t>44,22; 50,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,35; 42,02</t>
+          <t>36,24; 42,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,68; 39,5</t>
+          <t>31,63; 39,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,08; 42,75</t>
+          <t>30,23; 43,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,52; 47,1</t>
+          <t>32,75; 47,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 35,48</t>
+          <t>22,16; 35,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 30,73</t>
+          <t>17,21; 29,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,49; 40,66</t>
+          <t>26,03; 39,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,33; 56,55</t>
+          <t>41,45; 56,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,89; 51,45</t>
+          <t>37,08; 51,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,1; 38,64</t>
+          <t>23,91; 37,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,29; 39,88</t>
+          <t>30,59; 40,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,47; 49,56</t>
+          <t>39,15; 49,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,56; 41,16</t>
+          <t>31,72; 41,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 32,01</t>
+          <t>22,73; 31,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,29; 38,59</t>
+          <t>32,38; 38,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,97; 45,71</t>
+          <t>38,24; 45,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,75; 38,2</t>
+          <t>31,34; 38,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,34; 31,9</t>
+          <t>23,85; 32,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,26; 48,48</t>
+          <t>42,27; 48,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,22; 54,2</t>
+          <t>47,09; 54,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,18; 48,25</t>
+          <t>41,28; 48,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,86; 42,9</t>
+          <t>35,21; 43,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,08; 42,61</t>
+          <t>38,2; 42,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,31; 49,18</t>
+          <t>43,91; 48,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,54; 42,22</t>
+          <t>37,7; 42,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 36,74</t>
+          <t>30,83; 36,93</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24602</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29945</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27327</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17913</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34384</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29244</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28322</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>18036</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>58986</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59189</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55648</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>35949</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>18528; 31915</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23597; 36734</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21577; 32835</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9838; 26210</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28285; 41376</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22970; 36576</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22174; 34688</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12242; 24630</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>49262; 68979</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>49789; 67948</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47818; 62881</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>26836; 46339</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>125755</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>144001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>126505</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112628</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>198190</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>187390</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>173046</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>191017</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>323945</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>331390</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>299551</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>303645</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>111446; 141014</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>128622; 158047</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110349; 141522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>88057; 129876</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>183397; 214765</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>170630; 202037</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>155894; 189623</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>166750; 212401</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>302500; 345133</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>309659; 352226</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>277195; 322386</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>267354; 334991</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>53368</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48220</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36034</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31045</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42416</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64357</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59805</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>45547</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>95784</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>112578</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>95839</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>76593</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>44335; 63354</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39983; 57999</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28055; 44522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23036; 39578</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>32983; 49923</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>54212; 73865</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>50402; 69624</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>35485; 55559</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>83618; 109436</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>99003; 125334</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>83275; 109494</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>64173; 89516</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>203724</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>222166</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>189866</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161585</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>254601</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>478715</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>503157</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>451038</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>416187</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>187155; 221822</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201556; 239622</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170642; 208172</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>136889; 184399</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>255946; 295496</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>261798; 301889</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>241033; 280406</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>229878; 282178</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>452143; 506013</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>475509; 528149</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>425364; 481685</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>378202; 453025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,35; 40,23</t>
+          <t>23,54; 39,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,96; 54,42</t>
+          <t>34,25; 53,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,99; 69,99</t>
+          <t>47,08; 69,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,87; 55,61</t>
+          <t>21,7; 54,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,17; 60,22</t>
+          <t>41,07; 60,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,8; 58,59</t>
+          <t>37,91; 58,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,09; 64,27</t>
+          <t>42,17; 64,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,51; 47,3</t>
+          <t>24,38; 47,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,27; 46,59</t>
+          <t>33,48; 46,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,32; 52,29</t>
+          <t>38,26; 52,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,4; 62,33</t>
+          <t>47,31; 63,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,05; 46,71</t>
+          <t>26,7; 48,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,65; 40,05</t>
+          <t>31,89; 39,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,12; 46,84</t>
+          <t>38,36; 47,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 38,16</t>
+          <t>30,31; 38,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,41; 33,05</t>
+          <t>22,25; 32,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,73; 52,38</t>
+          <t>44,18; 51,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,04; 55,7</t>
+          <t>47,18; 55,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,56; 48,12</t>
+          <t>39,88; 48,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,86; 46,95</t>
+          <t>37,43; 47,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,69; 45,29</t>
+          <t>39,67; 45,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,22; 50,3</t>
+          <t>44,35; 50,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 42,15</t>
+          <t>36,48; 42,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,63; 39,63</t>
+          <t>31,34; 39,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 43,2</t>
+          <t>29,89; 43,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,75; 47,51</t>
+          <t>32,44; 47,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,16; 35,16</t>
+          <t>22,77; 36,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 29,56</t>
+          <t>17,34; 29,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,03; 39,4</t>
+          <t>27,14; 40,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,45; 56,47</t>
+          <t>41,85; 56,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,08; 51,22</t>
+          <t>36,68; 51,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,91; 37,44</t>
+          <t>24,33; 37,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,59; 40,04</t>
+          <t>30,25; 39,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,15; 49,56</t>
+          <t>39,92; 49,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,72; 41,7</t>
+          <t>32,02; 41,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,73; 31,71</t>
+          <t>23,11; 32,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,38; 38,37</t>
+          <t>32,24; 38,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,24; 45,47</t>
+          <t>38,77; 45,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,34; 38,24</t>
+          <t>31,33; 38,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 32,13</t>
+          <t>23,79; 32,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,27; 48,81</t>
+          <t>41,92; 48,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,09; 54,3</t>
+          <t>46,89; 54,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,28; 48,02</t>
+          <t>41,36; 48,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,21; 43,22</t>
+          <t>35,05; 42,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,2; 42,75</t>
+          <t>38,05; 42,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43,91; 48,77</t>
+          <t>43,98; 49,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 42,69</t>
+          <t>37,46; 42,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,83; 36,93</t>
+          <t>30,89; 36,59</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18528; 31915</t>
+          <t>18674; 31084</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23597; 36734</t>
+          <t>23118; 36258</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21577; 32835</t>
+          <t>22090; 32619</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9838; 26210</t>
+          <t>10227; 25799</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28285; 41376</t>
+          <t>28220; 41364</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22970; 36576</t>
+          <t>23664; 36399</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22174; 34688</t>
+          <t>22761; 35040</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12242; 24630</t>
+          <t>12695; 24701</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49262; 68979</t>
+          <t>49565; 69387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49789; 67948</t>
+          <t>49718; 68456</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47818; 62881</t>
+          <t>47727; 64117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26836; 46339</t>
+          <t>26490; 47615</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>111446; 141014</t>
+          <t>112282; 140288</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128622; 158047</t>
+          <t>129439; 159603</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110349; 141522</t>
+          <t>112405; 142085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88057; 129876</t>
+          <t>87441; 128619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>183397; 214765</t>
+          <t>181156; 213176</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>170630; 202037</t>
+          <t>171135; 203064</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>155894; 189623</t>
+          <t>157143; 189664</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>166750; 212401</t>
+          <t>169339; 215052</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>302500; 345133</t>
+          <t>302363; 346194</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>309659; 352226</t>
+          <t>310538; 354625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277195; 322386</t>
+          <t>279021; 321491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>267354; 334991</t>
+          <t>264947; 333492</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44335; 63354</t>
+          <t>43833; 63367</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39983; 57999</t>
+          <t>39602; 57473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28055; 44522</t>
+          <t>28837; 45615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23036; 39578</t>
+          <t>23216; 39252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32983; 49923</t>
+          <t>34388; 51314</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54212; 73865</t>
+          <t>54742; 73284</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50402; 69624</t>
+          <t>49861; 69557</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35485; 55559</t>
+          <t>36110; 56087</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83618; 109436</t>
+          <t>82675; 108050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99003; 125334</t>
+          <t>100957; 125271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83275; 109494</t>
+          <t>84065; 109123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64173; 89516</t>
+          <t>65240; 91376</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>187155; 221822</t>
+          <t>186354; 221172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>201556; 239622</t>
+          <t>204318; 242337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170642; 208172</t>
+          <t>170586; 208083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136889; 184399</t>
+          <t>136551; 184022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>255946; 295496</t>
+          <t>253811; 293625</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>261798; 301889</t>
+          <t>260692; 300656</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>241033; 280406</t>
+          <t>241538; 281183</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>229878; 282178</t>
+          <t>228801; 279715</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>452143; 506013</t>
+          <t>450305; 505438</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475509; 528149</t>
+          <t>476298; 532717</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>425364; 481685</t>
+          <t>422726; 477154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>378202; 453025</t>
+          <t>379010; 448946</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31,01%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>44,36%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>58,25%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,54; 39,18</t>
+          <t>40,72; 59,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,25; 53,71</t>
+          <t>36,21; 56,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,08; 69,53</t>
+          <t>41,54; 63,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 54,74</t>
+          <t>24,9; 49,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,07; 60,2</t>
+          <t>22,65; 39,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,91; 58,31</t>
+          <t>34,43; 54,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,17; 64,93</t>
+          <t>46,21; 68,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 47,43</t>
+          <t>21,95; 49,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,48; 46,87</t>
+          <t>33,34; 46,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,26; 52,69</t>
+          <t>38,83; 52,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,31; 63,55</t>
+          <t>47,17; 63,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 48,0</t>
+          <t>27,48; 45,23</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>35,72%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>42,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>34,11%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,92%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,89; 39,84</t>
+          <t>44,44; 52,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,36; 47,3</t>
+          <t>47,05; 55,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 38,31</t>
+          <t>39,25; 47,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 32,73</t>
+          <t>37,69; 48,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,18; 51,99</t>
+          <t>31,81; 40,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,18; 55,98</t>
+          <t>38,1; 46,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,88; 48,14</t>
+          <t>30,27; 38,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,43; 47,54</t>
+          <t>26,24; 34,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,67; 45,42</t>
+          <t>39,62; 45,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,35; 50,65</t>
+          <t>44,36; 50,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,48; 42,03</t>
+          <t>36,35; 42,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,34; 39,45</t>
+          <t>33,6; 40,21</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43,99%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>39,5%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28,46%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,89; 43,21</t>
+          <t>27,49; 40,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,44; 47,08</t>
+          <t>42,33; 56,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 36,03</t>
+          <t>36,89; 51,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 29,32</t>
+          <t>24,85; 38,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,14; 40,5</t>
+          <t>30,08; 42,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,85; 56,03</t>
+          <t>31,52; 47,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,68; 51,17</t>
+          <t>22,39; 35,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,33; 37,79</t>
+          <t>16,58; 29,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,25; 39,53</t>
+          <t>30,29; 39,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,92; 49,54</t>
+          <t>39,47; 49,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,02; 41,56</t>
+          <t>31,56; 41,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 32,37</t>
+          <t>22,34; 31,74</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,24; 38,26</t>
+          <t>42,26; 48,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,98</t>
+          <t>47,22; 54,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,33; 38,22</t>
+          <t>41,18; 48,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 32,06</t>
+          <t>35,32; 43,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,92; 48,5</t>
+          <t>32,29; 38,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,89; 54,08</t>
+          <t>38,97; 45,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,36; 48,15</t>
+          <t>31,75; 38,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,05; 42,85</t>
+          <t>25,21; 31,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,05; 42,71</t>
+          <t>38,08; 42,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43,98; 49,19</t>
+          <t>44,31; 49,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,46; 42,29</t>
+          <t>37,54; 42,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,89; 36,59</t>
+          <t>31,87; 36,78</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34384</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29244</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28322</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>24602</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>29945</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>27327</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17913</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34384</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29244</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28322</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>31413</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18674; 31084</t>
+          <t>27978; 40719</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23118; 36258</t>
+          <t>22605; 35403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22090; 32619</t>
+          <t>22419; 34274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10227; 25799</t>
+          <t>12050; 23768</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28220; 41364</t>
+          <t>17969; 31338</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23664; 36399</t>
+          <t>23244; 36832</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22761; 35040</t>
+          <t>21679; 32190</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12695; 24701</t>
+          <t>8750; 19634</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49565; 69387</t>
+          <t>49351; 69231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49718; 68456</t>
+          <t>50455; 67999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47727; 64117</t>
+          <t>47590; 63847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26490; 47615</t>
+          <t>24255; 39924</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>166</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>198190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>187390</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>173046</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>178873</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>125755</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>144001</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>126505</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>112628</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>198190</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>187390</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>173046</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>191017</t>
+          <t>110861</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>289734</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112282; 140288</t>
+          <t>182212; 214678</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>129439; 159603</t>
+          <t>170684; 202764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112405; 142085</t>
+          <t>154659; 188707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87441; 128619</t>
+          <t>158257; 202661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>181156; 213176</t>
+          <t>112000; 141238</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>171135; 203064</t>
+          <t>128551; 158155</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>157143; 189664</t>
+          <t>112271; 142278</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>169339; 215052</t>
+          <t>97033; 125999</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>302363; 346194</t>
+          <t>301966; 344158</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>310538; 354625</t>
+          <t>310597; 352177</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279021; 321491</t>
+          <t>278038; 321409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>264947; 333492</t>
+          <t>265367; 317506</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42416</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64357</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42896</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>53368</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>48220</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>36034</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31045</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42416</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64357</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59805</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45547</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76593</t>
+          <t>72979</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43833; 63367</t>
+          <t>34831; 51518</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39602; 57473</t>
+          <t>55373; 73961</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28837; 45615</t>
+          <t>50143; 69943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23216; 39252</t>
+          <t>34536; 53776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34388; 51314</t>
+          <t>44111; 62689</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54742; 73284</t>
+          <t>38483; 57493</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49861; 69557</t>
+          <t>28356; 44930</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36110; 56087</t>
+          <t>22341; 39531</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82675; 108050</t>
+          <t>82810; 109022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100957; 125271</t>
+          <t>99803; 125316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84065; 109123</t>
+          <t>82862; 108073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65240; 91376</t>
+          <t>61134; 86879</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>233</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161585</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155007</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>416187</t>
+          <t>394126</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186354; 221172</t>
+          <t>255865; 293526</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204318; 242337</t>
+          <t>262542; 301350</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170586; 208083</t>
+          <t>240456; 281764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136551; 184022</t>
+          <t>214496; 262239</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>253811; 293625</t>
+          <t>186635; 223096</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>260692; 300656</t>
+          <t>205399; 240883</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>241538; 281183</t>
+          <t>172831; 207961</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>228801; 279715</t>
+          <t>137244; 173543</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>450305; 505438</t>
+          <t>450692; 504253</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>476298; 532717</t>
+          <t>479824; 532637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>422726; 477154</t>
+          <t>423582; 476396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>379010; 448946</t>
+          <t>367009; 423614</t>
         </is>
       </c>
     </row>
